--- a/ejemplo/plantilla_participantes.xlsx
+++ b/ejemplo/plantilla_participantes.xlsx
@@ -644,12 +644,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>Opcional</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nombre que saldrá en la matriz y en el Excel</t>
+          <t>Solo para identificarlo en la matriz y el Excel. Puede ir vacío</t>
         </is>
       </c>
     </row>

--- a/ejemplo/plantilla_participantes.xlsx
+++ b/ejemplo/plantilla_participantes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -553,35 +553,56 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Vendedor</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40687294</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>41544805</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Carlos Soto</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Líder</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>LORETO</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" t="n">
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" t="n">
         <v>30</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -594,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -627,12 +648,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Obligatorio</t>
+          <t>Obligatorio*</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>El número que sale en LOGIN (vendedor) o LEADER (líder) del Fanero</t>
+          <t>El número que sale en LOGIN (vendedor) o LEADER (líder) del Fanero. *Puede ir vacío si llenas DNI_LIDER (ver abajo)</t>
         </is>
       </c>
     </row>
@@ -700,7 +721,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Solo vendedores: DNI de su líder. Vacío = el que figura en el Fanero</t>
+          <t>Vendedor CON DNI: su líder (vacío = el del Fanero). Vendedor SIN DNI: participan TODOS los vendedores de ese líder según el Fanero, cada uno con su DNI. Líder sin DNI: se toma este número como su DNI</t>
         </is>
       </c>
     </row>
@@ -782,6 +803,19 @@
       <c r="C11" t="inlineStr">
         <is>
           <t>Solo se usan las cuotas de los productos que tenga el incentivo. Una cuota 0 = ese producto no se le exige</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Nota</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Si un vendedor está con su DNI y también entra por el equipo de su líder, vale su fila con DNI</t>
         </is>
       </c>
     </row>
